--- a/AtchisonRegime/Outputs/USA/USA500/df_TESTCONTOUR_rawData.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500/df_TESTCONTOUR_rawData.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD686"/>
+  <dimension ref="A1:AD687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66337,6 +66337,102 @@
       </c>
       <c r="AD686" t="n">
         <v>-0</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="n">
+        <v>685</v>
+      </c>
+      <c r="B687" s="2" t="n">
+        <v>45473</v>
+      </c>
+      <c r="C687" t="n">
+        <v>-1.13653593688915</v>
+      </c>
+      <c r="D687" t="n">
+        <v>0.06227684249567139</v>
+      </c>
+      <c r="E687" t="b">
+        <v>0</v>
+      </c>
+      <c r="F687" t="b">
+        <v>1</v>
+      </c>
+      <c r="G687" t="n">
+        <v>3.550584118834532</v>
+      </c>
+      <c r="H687" t="n">
+        <v>29102797.58239391</v>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="K687" t="n">
+        <v>0</v>
+      </c>
+      <c r="L687" t="n">
+        <v>0</v>
+      </c>
+      <c r="M687" t="n">
+        <v>3.550584118834532</v>
+      </c>
+      <c r="N687" t="n">
+        <v>0</v>
+      </c>
+      <c r="O687" t="n">
+        <v>598.8102026084118</v>
+      </c>
+      <c r="P687" t="n">
+        <v>66.71958563839446</v>
+      </c>
+      <c r="Q687" t="n">
+        <v>2559.928408241826</v>
+      </c>
+      <c r="R687" t="n">
+        <v>278.8166411603501</v>
+      </c>
+      <c r="S687" t="n">
+        <v>12</v>
+      </c>
+      <c r="T687" t="n">
+        <v>0</v>
+      </c>
+      <c r="U687" t="n">
+        <v>0</v>
+      </c>
+      <c r="V687" t="n">
+        <v>0</v>
+      </c>
+      <c r="W687" t="n">
+        <v>0</v>
+      </c>
+      <c r="X687" t="n">
+        <v>3.550584118834532</v>
+      </c>
+      <c r="Y687" t="n">
+        <v>26.46032897183035</v>
+      </c>
+      <c r="Z687" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA687" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB687" t="n">
+        <v>9.627802909711637</v>
+      </c>
+      <c r="AC687" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AD687" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -66620,13 +66716,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D19CCECE-0F57-4D4E-91E7-D44E1E60732B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8021E1F-6170-4303-871A-A03DBF5684F9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AD32397-F385-43BE-B003-74BF61BF3B35}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2E50F80-900D-43A9-913B-126C22196ED1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB6ED3F5-1A3D-4E58-9E8D-91AF24223534}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EE88872-C714-4DCA-B8AA-31181C8BD65E}"/>
 </file>
--- a/AtchisonRegime/Outputs/USA/USA500/df_TESTCONTOUR_rawData.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500/df_TESTCONTOUR_rawData.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD687"/>
+  <dimension ref="A1:AD688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66330,7 +66330,7 @@
         <v>0</v>
       </c>
       <c r="AB686" t="n">
-        <v>6.385706942424463</v>
+        <v>6.793937488667878</v>
       </c>
       <c r="AC686" t="n">
         <v>-1.1</v>
@@ -66426,13 +66426,109 @@
         <v>0</v>
       </c>
       <c r="AB687" t="n">
-        <v>9.627802909711637</v>
+        <v>13.33306113186874</v>
       </c>
       <c r="AC687" t="n">
         <v>-1.1</v>
       </c>
       <c r="AD687" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="n">
+        <v>686</v>
+      </c>
+      <c r="B688" s="2" t="n">
+        <v>45504</v>
+      </c>
+      <c r="C688" t="n">
+        <v>-1.151360964367</v>
+      </c>
+      <c r="D688" t="n">
+        <v>-0.05308453772626753</v>
+      </c>
+      <c r="E688" t="b">
+        <v>0</v>
+      </c>
+      <c r="F688" t="b">
+        <v>1</v>
+      </c>
+      <c r="G688" t="n">
+        <v>2.379661281418732</v>
+      </c>
+      <c r="H688" t="n">
+        <v>29795345.58827181</v>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="K688" t="n">
+        <v>0</v>
+      </c>
+      <c r="L688" t="n">
+        <v>0</v>
+      </c>
+      <c r="M688" t="n">
+        <v>2.379661281418732</v>
+      </c>
+      <c r="N688" t="n">
+        <v>0</v>
+      </c>
+      <c r="O688" t="n">
+        <v>598.8102026084118</v>
+      </c>
+      <c r="P688" t="n">
+        <v>66.71958563839446</v>
+      </c>
+      <c r="Q688" t="n">
+        <v>2620.846033404795</v>
+      </c>
+      <c r="R688" t="n">
+        <v>278.8166411603501</v>
+      </c>
+      <c r="S688" t="n">
+        <v>13</v>
+      </c>
+      <c r="T688" t="n">
+        <v>0</v>
+      </c>
+      <c r="U688" t="n">
+        <v>0</v>
+      </c>
+      <c r="V688" t="n">
+        <v>0</v>
+      </c>
+      <c r="W688" t="n">
+        <v>0</v>
+      </c>
+      <c r="X688" t="n">
+        <v>2.379661281418732</v>
+      </c>
+      <c r="Y688" t="n">
+        <v>29.46965645672774</v>
+      </c>
+      <c r="Z688" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA688" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB688" t="n">
+        <v>19.07175616788135</v>
+      </c>
+      <c r="AC688" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AD688" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>
@@ -66716,13 +66812,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8021E1F-6170-4303-871A-A03DBF5684F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5739A376-2D62-4B93-8A95-DCDDC3B27DCB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2E50F80-900D-43A9-913B-126C22196ED1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13773B9C-7C6A-4C0A-AA17-67ADB10F81B7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EE88872-C714-4DCA-B8AA-31181C8BD65E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A782262-179A-4D7C-9F08-072BD779AC96}"/>
 </file>
--- a/AtchisonRegime/Outputs/USA/USA500/df_TESTCONTOUR_rawData.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500/df_TESTCONTOUR_rawData.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD688"/>
+  <dimension ref="A1:AD691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66529,6 +66529,294 @@
       </c>
       <c r="AD688" t="n">
         <v>-0.1</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="n">
+        <v>687</v>
+      </c>
+      <c r="B689" s="2" t="n">
+        <v>45535</v>
+      </c>
+      <c r="C689" t="n">
+        <v>-1.199054339561413</v>
+      </c>
+      <c r="D689" t="n">
+        <v>0.05734064607590641</v>
+      </c>
+      <c r="E689" t="b">
+        <v>0</v>
+      </c>
+      <c r="F689" t="b">
+        <v>1</v>
+      </c>
+      <c r="G689" t="n">
+        <v>-0.9706105355517303</v>
+      </c>
+      <c r="H689" t="n">
+        <v>29506148.82488799</v>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="K689" t="n">
+        <v>0</v>
+      </c>
+      <c r="L689" t="n">
+        <v>0</v>
+      </c>
+      <c r="M689" t="n">
+        <v>-0.9706105355517303</v>
+      </c>
+      <c r="N689" t="n">
+        <v>0</v>
+      </c>
+      <c r="O689" t="n">
+        <v>598.8102026084118</v>
+      </c>
+      <c r="P689" t="n">
+        <v>66.71958563839446</v>
+      </c>
+      <c r="Q689" t="n">
+        <v>2595.407825683979</v>
+      </c>
+      <c r="R689" t="n">
+        <v>278.8166411603501</v>
+      </c>
+      <c r="S689" t="n">
+        <v>14</v>
+      </c>
+      <c r="T689" t="n">
+        <v>0</v>
+      </c>
+      <c r="U689" t="n">
+        <v>0</v>
+      </c>
+      <c r="V689" t="n">
+        <v>0</v>
+      </c>
+      <c r="W689" t="n">
+        <v>0</v>
+      </c>
+      <c r="X689" t="n">
+        <v>-0.9706105355517303</v>
+      </c>
+      <c r="Y689" t="n">
+        <v>28.21301033081611</v>
+      </c>
+      <c r="Z689" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA689" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB689" t="n">
+        <v>26.53182250092929</v>
+      </c>
+      <c r="AC689" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AD689" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="n">
+        <v>688</v>
+      </c>
+      <c r="B690" s="2" t="n">
+        <v>45565</v>
+      </c>
+      <c r="C690" t="n">
+        <v>-1.211312601852137</v>
+      </c>
+      <c r="D690" t="n">
+        <v>0.1339068761472364</v>
+      </c>
+      <c r="E690" t="b">
+        <v>0</v>
+      </c>
+      <c r="F690" t="b">
+        <v>1</v>
+      </c>
+      <c r="G690" t="n">
+        <v>2.722110622953977</v>
+      </c>
+      <c r="H690" t="n">
+        <v>30309338.83647488</v>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="K690" t="n">
+        <v>0</v>
+      </c>
+      <c r="L690" t="n">
+        <v>0</v>
+      </c>
+      <c r="M690" t="n">
+        <v>2.722110622953977</v>
+      </c>
+      <c r="N690" t="n">
+        <v>0</v>
+      </c>
+      <c r="O690" t="n">
+        <v>598.8102026084118</v>
+      </c>
+      <c r="P690" t="n">
+        <v>66.71958563839446</v>
+      </c>
+      <c r="Q690" t="n">
+        <v>2666.057697815902</v>
+      </c>
+      <c r="R690" t="n">
+        <v>278.8166411603501</v>
+      </c>
+      <c r="S690" t="n">
+        <v>15</v>
+      </c>
+      <c r="T690" t="n">
+        <v>0</v>
+      </c>
+      <c r="U690" t="n">
+        <v>0</v>
+      </c>
+      <c r="V690" t="n">
+        <v>0</v>
+      </c>
+      <c r="W690" t="n">
+        <v>0</v>
+      </c>
+      <c r="X690" t="n">
+        <v>2.722110622953977</v>
+      </c>
+      <c r="Y690" t="n">
+        <v>31.70311030504034</v>
+      </c>
+      <c r="Z690" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA690" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB690" t="n">
+        <v>39.0081791823224</v>
+      </c>
+      <c r="AC690" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AD690" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="n">
+        <v>689</v>
+      </c>
+      <c r="B691" s="2" t="n">
+        <v>45596</v>
+      </c>
+      <c r="C691" t="n">
+        <v>-1.189056899431358</v>
+      </c>
+      <c r="D691" t="n">
+        <v>0.2044769373519747</v>
+      </c>
+      <c r="E691" t="b">
+        <v>0</v>
+      </c>
+      <c r="F691" t="b">
+        <v>1</v>
+      </c>
+      <c r="G691" t="n">
+        <v>3.151886162971063</v>
+      </c>
+      <c r="H691" t="n">
+        <v>31264654.69334974</v>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="K691" t="n">
+        <v>0</v>
+      </c>
+      <c r="L691" t="n">
+        <v>0</v>
+      </c>
+      <c r="M691" t="n">
+        <v>3.151886162971063</v>
+      </c>
+      <c r="N691" t="n">
+        <v>0</v>
+      </c>
+      <c r="O691" t="n">
+        <v>598.8102026084118</v>
+      </c>
+      <c r="P691" t="n">
+        <v>66.71958563839446</v>
+      </c>
+      <c r="Q691" t="n">
+        <v>2750.088801490186</v>
+      </c>
+      <c r="R691" t="n">
+        <v>278.8166411603501</v>
+      </c>
+      <c r="S691" t="n">
+        <v>16</v>
+      </c>
+      <c r="T691" t="n">
+        <v>0</v>
+      </c>
+      <c r="U691" t="n">
+        <v>0</v>
+      </c>
+      <c r="V691" t="n">
+        <v>0</v>
+      </c>
+      <c r="W691" t="n">
+        <v>0</v>
+      </c>
+      <c r="X691" t="n">
+        <v>3.151886162971063</v>
+      </c>
+      <c r="Y691" t="n">
+        <v>35.85424241494741</v>
+      </c>
+      <c r="Z691" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA691" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB691" t="n">
+        <v>47.22484755237713</v>
+      </c>
+      <c r="AC691" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AD691" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -66812,13 +67100,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5739A376-2D62-4B93-8A95-DCDDC3B27DCB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0049B6-85ED-4B19-93F6-A64AE8516002}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13773B9C-7C6A-4C0A-AA17-67ADB10F81B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9477E16-FDB3-469C-B9FE-C1C2E1E6EF1E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A782262-179A-4D7C-9F08-072BD779AC96}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{323600AB-6CD9-4B92-A46F-CE855A657EAA}"/>
 </file>